--- a/quizzes/sculpture-18e-niveau1.xlsx
+++ b/quizzes/sculpture-18e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E11CC709-470C-4A84-A843-141EA8A3C1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB16E52-B818-40D1-A1C8-E56EC4C0F877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -124,9 +124,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Bust_of_Louis_XV_by_Jean-Baptiste_Lemoyne_the_Younger_%281749%29.jpg/1280px-Bust_of_Louis_XV_by_Jean-Baptiste_Lemoyne_the_Younger_%281749%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Jean-Baptiste II LEMOYNE</t>
-  </si>
-  <si>
     <t>1749</t>
   </si>
   <si>
@@ -455,6 +452,9 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Pudicizia%2C_Cappella_Sansevero.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Jean-Baptiste LEMOYNE</t>
   </si>
 </sst>
 </file>
@@ -928,7 +928,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>10</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>14</v>
@@ -979,7 +979,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>22</v>
@@ -988,15 +988,15 @@
         <v>23</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>136</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>24</v>
@@ -1033,390 +1033,390 @@
         <v>33</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>16</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="C11" s="5" t="s">
         <v>42</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>43</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C12" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="C13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="E15" s="5" t="s">
         <v>63</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="C16" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="C17" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>73</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="C18" s="5" t="s">
         <v>76</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="C19" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="C21" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="C22" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="D22" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="C24" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="D24" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>104</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C25" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="D25" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="C26" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" s="5" t="s">
         <v>112</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="C27" s="5" t="s">
         <v>115</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>116</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="C28" s="5" t="s">
         <v>119</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>120</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B29" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B30" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="C30" s="5" t="s">
         <v>127</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>128</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B31" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="C31" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/quizzes/sculpture-18e-niveau1.xlsx
+++ b/quizzes/sculpture-18e-niveau1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\Codex\2026-08-11\referenced-chatgpt-conversation-this-is-an\outputs\quiz-art-excel\fichiers excel terminés\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB16E52-B818-40D1-A1C8-E56EC4C0F877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF2DE037-967F-42A2-AD08-C94DC2310FB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="216">
   <si>
     <t>image</t>
   </si>
@@ -37,6 +37,18 @@
     <t>titre de l'œuvre</t>
   </si>
   <si>
+    <t>dates artiste</t>
+  </si>
+  <si>
+    <t>Matériaux et technique</t>
+  </si>
+  <si>
+    <t>Dimensions</t>
+  </si>
+  <si>
+    <t>Nationalité</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/4/4e/Jean-Antoine_Houdon%2C_voltaire%2C_1781.JPG/1280px-Jean-Antoine_Houdon%2C_voltaire%2C_1781.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -52,6 +64,21 @@
     <t>Voltaire assis</t>
   </si>
   <si>
+    <t>1741-1828</t>
+  </si>
+  <si>
+    <t>Marbre</t>
+  </si>
+  <si>
+    <t>environ 130 cm de haut (assis)</t>
+  </si>
+  <si>
+    <t>française</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3e/Bronze_Horseman_02.jpg/1280px-Bronze_Horseman_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>Étienne Maurice FALCONET</t>
   </si>
   <si>
@@ -64,6 +91,18 @@
     <t>Le Cavalier de bronze (statue équestre de Pierre le Grand)</t>
   </si>
   <si>
+    <t>1716-1791</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+  </si>
+  <si>
+    <t>dimensions monumentales</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/88/Mercury_Pigalle_Louvre_RF3023.jpg/960px-Mercury_Pigalle_Louvre_RF3023.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>Jean-Baptiste PIGALLE</t>
   </si>
   <si>
@@ -76,6 +115,12 @@
     <t>Mercure attachant ses talonnières</t>
   </si>
   <si>
+    <t>1714-1785</t>
+  </si>
+  <si>
+    <t>59 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ef/0_Psych%C3%A9_ranim%C3%A9e_par_le_baiser_de_l%27Amour_-_Canova_-_Louvre_1.JPG/1280px-0_Psych%C3%A9_ranim%C3%A9e_par_le_baiser_de_l%27Amour_-_Canova_-_Louvre_1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -88,12 +133,45 @@
     <t>Psyché ranimée par le baiser de l'Amour</t>
   </si>
   <si>
+    <t>1757-1822</t>
+  </si>
+  <si>
+    <t>155 × 168 cm</t>
+  </si>
+  <si>
+    <t>italienne</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/8/8b/Messerschmidt%2C_Yawning.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
     <t>Franz Xaver MESSERSCHMIDT</t>
   </si>
   <si>
     <t>1770-1783</t>
   </si>
   <si>
+    <t>Musée des Beaux Arts, Budapest</t>
+  </si>
+  <si>
+    <t>L'Homme qui bäille (sérieTêtes de caractère)</t>
+  </si>
+  <si>
+    <t>1736-1783</t>
+  </si>
+  <si>
+    <t>Alliage plomb-étain</t>
+  </si>
+  <si>
+    <t>environ 40 cm de haut</t>
+  </si>
+  <si>
+    <t>autrichienne</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/72/Louis-Fran%C3%A7ois_Roubiliac-George_Frederick_Handel-Victoria_and_Albert_Museum.jpg/960px-Louis-Fran%C3%A7ois_Roubiliac-George_Frederick_Handel-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>Louis-François ROUBILIAC</t>
   </si>
   <si>
@@ -106,6 +184,12 @@
     <t>Monument à Georg Friedrich Haendel</t>
   </si>
   <si>
+    <t>1702-1762</t>
+  </si>
+  <si>
+    <t>environ 220 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/32/Satyr_and_Bacchante_by_Clodion_%281780%29.jpg/1280px-Satyr_and_Bacchante_by_Clodion_%281780%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -121,9 +205,21 @@
     <t>Satyre et Bacchante</t>
   </si>
   <si>
+    <t>1738-1814</t>
+  </si>
+  <si>
+    <t>Terre cuite</t>
+  </si>
+  <si>
+    <t>environ 34 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/12/Bust_of_Louis_XV_by_Jean-Baptiste_Lemoyne_the_Younger_%281749%29.jpg/1280px-Bust_of_Louis_XV_by_Jean-Baptiste_Lemoyne_the_Younger_%281749%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>Jean-Baptiste LEMOYNE</t>
+  </si>
+  <si>
     <t>1749</t>
   </si>
   <si>
@@ -133,6 +229,15 @@
     <t>Buste de Louis XV</t>
   </si>
   <si>
+    <t>1704-1778</t>
+  </si>
+  <si>
+    <t>environ 80 cm de haut</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Louvre_amour_arc_mr1761.jpg/960px-Louvre_amour_arc_mr1761.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
     <t>Edme BOUCHARDON</t>
   </si>
   <si>
@@ -142,6 +247,12 @@
     <t>L'Amour se faisant un arc de la massue d'Hercule</t>
   </si>
   <si>
+    <t>1698-1762</t>
+  </si>
+  <si>
+    <t>173 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/76/Marly_horse_Louvre_MR1802.jpg/1280px-Marly_horse_Louvre_MR1802.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -154,6 +265,9 @@
     <t>Cheval retenu par un palefrenier (Chevaux de Marly)</t>
   </si>
   <si>
+    <t>1677-1746</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Psyche_Abandoned_LACMA_M.76.78.jpg/1280px-Psyche_Abandoned_LACMA_M.76.78.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -169,6 +283,12 @@
     <t>Psyché abandonnée</t>
   </si>
   <si>
+    <t>1730-1809</t>
+  </si>
+  <si>
+    <t>175 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3a/Ignaz_Guenther_Schutzengel_Buergersaal_Muenchen-1.jpg/1280px-Ignaz_Guenther_Schutzengel_Buergersaal_Muenchen-1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -184,6 +304,18 @@
     <t>Ange gardien (Schutzengelgruppe)</t>
   </si>
   <si>
+    <t>1725-1775</t>
+  </si>
+  <si>
+    <t>Bois polychrome</t>
+  </si>
+  <si>
+    <t>dimensions architecturales</t>
+  </si>
+  <si>
+    <t>allemande</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/WA1216_99_Lower_Belvedere_Apotheosis_of_Prince_Eugene_of_Savoy_3D.jpg/1280px-WA1216_99_Lower_Belvedere_Apotheosis_of_Prince_Eugene_of_Savoy_3D.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -199,6 +331,12 @@
     <t>Apothéose du prince Eugène</t>
   </si>
   <si>
+    <t>1651-1732</t>
+  </si>
+  <si>
+    <t>environ 200 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/98/Schadow-Prinzessinnen.jpg/1280px-Schadow-Prinzessinnen.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -214,6 +352,12 @@
     <t>Le Groupe des princesses (Louise et Frédérique de Prusse)</t>
   </si>
   <si>
+    <t>1764-1850</t>
+  </si>
+  <si>
+    <t>172 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/16/Charles_James_Fox_by_Joseph_Nollekens_1792.jpg/1280px-Charles_James_Fox_by_Joseph_Nollekens_1792.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -229,6 +373,15 @@
     <t>Buste de Charles James Fox</t>
   </si>
   <si>
+    <t>1737-1823</t>
+  </si>
+  <si>
+    <t>environ 70 cm de haut</t>
+  </si>
+  <si>
+    <t>anglaise (Royaume-Uni)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8e/Detail_of_Newton_monument%2C_Westminster_Abbey.jpg/1280px-Detail_of_Newton_monument%2C_Westminster_Abbey.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -244,6 +397,12 @@
     <t>Monument à Isaac Newton</t>
   </si>
   <si>
+    <t>1694-1770</t>
+  </si>
+  <si>
+    <t>flamande (Belgique)</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/6c/Amalthea_Julien_Louvre_CC230.jpg/1280px-Amalthea_Julien_Louvre_CC230.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -256,6 +415,12 @@
     <t>Amalthée et la chèvre de Jupiter</t>
   </si>
   <si>
+    <t>1731-1804</t>
+  </si>
+  <si>
+    <t>87 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/88/Jean-Philippe_Rameau_by_Jean-Jacques_Caffieri_-_20080203-03.jpg/1280px-Jean-Philippe_Rameau_by_Jean-Jacques_Caffieri_-_20080203-03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -271,6 +436,15 @@
     <t>Buste de Jean-Philippe Rameau</t>
   </si>
   <si>
+    <t>1725-1792</t>
+  </si>
+  <si>
+    <t>environ 50 cm de haut</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d0/Rome_basilica_st_peter_015.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr</t>
+  </si>
+  <si>
     <t>Michel-Ange SLODTZ</t>
   </si>
   <si>
@@ -280,6 +454,12 @@
     <t>Saint Bruno</t>
   </si>
   <si>
+    <t>1705-1764</t>
+  </si>
+  <si>
+    <t>environ 300 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8b/Fd.4.8_Giacomo_Serpotta%2C_Oratorio_di_S._Cita_Palermo%2C_statua_allegorica_-FG.jpg/1280px-Fd.4.8_Giacomo_Serpotta%2C_Oratorio_di_S._Cita_Palermo%2C_statua_allegorica_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -295,6 +475,12 @@
     <t>Décors en stuc de l'Oratoire du Rosaire</t>
   </si>
   <si>
+    <t>1656-1732</t>
+  </si>
+  <si>
+    <t>Stuc</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/37/Abteikirche_Mari%C3%A4_Himmelfahrt_Rohr_Marienskulptur.jpg/1280px-Abteikirche_Mari%C3%A4_Himmelfahrt_Rohr_Marienskulptur.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -310,6 +496,12 @@
     <t>L'Assomption de la Vierge (maître-autel)</t>
   </si>
   <si>
+    <t>1692-1750</t>
+  </si>
+  <si>
+    <t>Stuc et bois polychrome</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/0/05/Francesco_Queirolo_-_Il_Disinganno_%281753-54%29_-_Detail.jpg/1280px-Francesco_Queirolo_-_Il_Disinganno_%281753-54%29_-_Detail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -325,6 +517,9 @@
     <t>Il Disinganno (Le Désabusement)</t>
   </si>
   <si>
+    <t>1704-1762</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/77/Giuseppe_Sanmartino_%28circle_of%29_-_Veiled_Christ.jpg/1280px-Giuseppe_Sanmartino_%28circle_of%29_-_Veiled_Christ.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -337,6 +532,15 @@
     <t>Le Christ voilé</t>
   </si>
   <si>
+    <t>1720-1793</t>
+  </si>
+  <si>
+    <t>170 cm de long (gisant)</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Pudicizia%2C_Cappella_Sansevero.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
     <t>Antonio CORRADINI</t>
   </si>
   <si>
@@ -346,6 +550,12 @@
     <t>La Pudicizia (La Pudeur)</t>
   </si>
   <si>
+    <t>1688-1752</t>
+  </si>
+  <si>
+    <t>environ 180 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/73/Mars_and_Venus%2C_1804_CE%2C_by_Johan_Tobias_Sergel._Nationalmuseum%2C_Sweden.jpg/1280px-Mars_and_Venus%2C_1804_CE%2C_by_Johan_Tobias_Sergel._Nationalmuseum%2C_Sweden.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -361,6 +571,15 @@
     <t>Mars et Vénus</t>
   </si>
   <si>
+    <t>1740-1814</t>
+  </si>
+  <si>
+    <t>environ 170 cm de haut</t>
+  </si>
+  <si>
+    <t>suédoise</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/93/Adam_-_Neptune_calmant_les_flots_01.jpg/1280px-Adam_-_Neptune_calmant_les_flots_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -373,6 +592,12 @@
     <t>Neptune calmant les flots</t>
   </si>
   <si>
+    <t>1700-1759</t>
+  </si>
+  <si>
+    <t>dimensions non standardisées</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/28/Prometheus_Adam_Louvre_MR1745_edit.jpg/1280px-Prometheus_Adam_Louvre_MR1745_edit.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -385,6 +610,12 @@
     <t>Prométhée enchaîné</t>
   </si>
   <si>
+    <t>1705-1778</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/1/1c/Archives_nationales_%28Paris%29_cour_des_chevaux_du_Soleil_%28Minutier_central_des_notaires_de_Paris%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
     <t>Robert LE LORRAIN</t>
   </si>
   <si>
@@ -397,6 +628,12 @@
     <t>Les Chevaux du Soleil</t>
   </si>
   <si>
+    <t>1666-1743</t>
+  </si>
+  <si>
+    <t>Plomb doré</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/1b/Bather_Allegrain_Louvre_MR1747.jpg/1280px-Bather_Allegrain_Louvre_MR1747.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -409,6 +646,12 @@
     <t>Vénus sortant du bain (La Baigneuse)</t>
   </si>
   <si>
+    <t>1710-1795</t>
+  </si>
+  <si>
+    <t>174 cm de haut</t>
+  </si>
+  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d1/Buste_d%27Etienne_Falconet_par_Marie-Anne_Collot.jpg/1280px-Buste_d%27Etienne_Falconet_par_Marie-Anne_Collot.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -424,45 +667,35 @@
     <t>Buste d'Étienne Maurice Falconet</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/8/8b/Messerschmidt%2C_Yawning.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Musée des Beaux Arts, Budapest</t>
-  </si>
-  <si>
-    <t>L'Homme qui bäille (sérieTêtes de caractère)</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/72/Louis-Fran%C3%A7ois_Roubiliac-George_Frederick_Handel-Victoria_and_Albert_Museum.jpg/960px-Louis-Fran%C3%A7ois_Roubiliac-George_Frederick_Handel-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/d/d0/Rome_basilica_st_peter_015.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/1/1c/Archives_nationales_%28Paris%29_cour_des_chevaux_du_Soleil_%28Minutier_central_des_notaires_de_Paris%29.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/3e/Bronze_Horseman_02.jpg/1280px-Bronze_Horseman_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/88/Mercury_Pigalle_Louvre_RF3023.jpg/960px-Mercury_Pigalle_Louvre_RF3023.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/38/Louvre_amour_arc_mr1761.jpg/960px-Louvre_amour_arc_mr1761.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Pudicizia%2C_Cappella_Sansevero.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
-  </si>
-  <si>
-    <t>Jean-Baptiste LEMOYNE</t>
+    <t>1748-1821</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="9">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -472,23 +705,29 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <name val="Carlito"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0563C1"/>
-      <name val="Carlito"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -503,18 +742,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC54F38"/>
+        <fgColor theme="0"/>
         <bgColor rgb="FFC54F38"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -523,62 +762,40 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FFA7402C"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FFA7402C"/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom style="medium">
-        <color rgb="FFA7402C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color rgb="FFA7402C"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFA7402C"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFA7402C"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFA7402C"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFA7402C"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -882,7 +1099,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="84.42578125" customWidth="1"/>
@@ -892,565 +1109,937 @@
     <col min="5" max="5" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:9" s="7" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="6" t="s">
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="6" t="s">
+      <c r="B20" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="7" t="s">
+      <c r="C20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="5" t="s">
+    <row r="21" spans="1:9">
+      <c r="A21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="4" t="s">
+      <c r="E27" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>133</v>
+      <c r="I29" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="A5" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="A8" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="A9" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="A11" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="A12" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="A13" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="A14" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="A15" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="A16" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="A17" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="A18" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="A19" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="A21" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="A22" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="A23" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="A24" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="A26" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="A27" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="A28" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="A30" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="A31" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="A6" r:id="rId23" xr:uid="{F8C8E37D-BC85-4683-BCDB-E3E712398F1D}"/>
-    <hyperlink ref="A7" r:id="rId24" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/72/Louis-Fran%C3%A7ois_Roubiliac-George_Frederick_Handel-Victoria_and_Albert_Museum.jpg/960px-Louis-Fran%C3%A7ois_Roubiliac-George_Frederick_Handel-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B8A5E6CB-C63A-45A8-976F-47762BCB8C54}"/>
-    <hyperlink ref="A20" r:id="rId25" xr:uid="{79102047-016B-4EDA-BD85-DA42336F5898}"/>
-    <hyperlink ref="A29" r:id="rId26" xr:uid="{E7F90237-FA85-4DA1-AF5D-3989FC66DEE3}"/>
-    <hyperlink ref="A3" r:id="rId27" xr:uid="{96229145-E20C-4328-B3B6-C89FB90FF6BE}"/>
-    <hyperlink ref="A4" r:id="rId28" xr:uid="{432B8222-DB0A-477F-9E2A-211485F2A10F}"/>
-    <hyperlink ref="A10" r:id="rId29" xr:uid="{BB56DA95-C2D8-4E1D-8209-BB9965AA041A}"/>
-    <hyperlink ref="A25" r:id="rId30" xr:uid="{930BAF17-9E04-404B-B8A5-820BA3EA6C67}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="A7" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/commons/thumb/7/72/Louis-Fran%C3%A7ois_Roubiliac-George_Frederick_Handel-Victoria_and_Albert_Museum.jpg/960px-Louis-Fran%C3%A7ois_Roubiliac-George_Frederick_Handel-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="A8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="A9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="A10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="A11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="A12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="A13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="A14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="A15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="A16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="A17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="A18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="A19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="A20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="A21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="A22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="A23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="A24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="A25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="A26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="A27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="A28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="A29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="A30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="A31" r:id="rId30" xr:uid="{00000000-0004-0000-0000-00001D000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
